--- a/xxv001 - resource shares by player.xlsx
+++ b/xxv001 - resource shares by player.xlsx
@@ -467,22 +467,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2901559084190664</v>
+        <v>0.3277573664868873</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1595735627684227</v>
+        <v>0.1719746407759634</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3633260452997296</v>
+        <v>0.332369516353919</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1828162616925818</v>
+        <v>0.161098600857303</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3465180462812041</v>
+        <v>0.3398731171591937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1696718671104088</v>
+        <v>0.1691597052817787</v>
       </c>
     </row>
     <row r="3">
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.308468329564574</v>
+        <v>0.3166895047258905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1926709915003422</v>
+        <v>0.2286506502421915</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4107957554926191</v>
+        <v>0.3147242667184303</v>
       </c>
       <c r="E3" t="n">
-        <v>0.249026852712876</v>
+        <v>0.2382071173545325</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2807359149428069</v>
+        <v>0.3685862285556791</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2247881231243659</v>
+        <v>0.2482605711113816</v>
       </c>
     </row>
     <row r="4">
@@ -517,22 +517,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3491479722547834</v>
+        <v>0.3753344544900797</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1709058115231287</v>
+        <v>0.2063281607390229</v>
       </c>
       <c r="D4" t="n">
-        <v>0.307717901809233</v>
+        <v>0.3417527532754221</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1957320025582341</v>
+        <v>0.1908319915795889</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3431341259359835</v>
+        <v>0.2829127922344982</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2027795567242727</v>
+        <v>0.1912118480889917</v>
       </c>
     </row>
     <row r="5">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3762953930351965</v>
+        <v>0.3133852369202236</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1948117279474867</v>
+        <v>0.1972630689862976</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3234531728323625</v>
+        <v>0.3503109046485213</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1732229577072523</v>
+        <v>0.1756348637517762</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3002514341324409</v>
+        <v>0.3363038584312551</v>
       </c>
       <c r="G5" t="n">
-        <v>0.19539430973054</v>
+        <v>0.2042565505682773</v>
       </c>
     </row>
     <row r="6">
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3567278538455009</v>
+        <v>0.3651208897377999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2060750660147243</v>
+        <v>0.2235530484016814</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2845690681867153</v>
+        <v>0.3017523353744809</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1775912249384443</v>
+        <v>0.1901966921666366</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3587030779677838</v>
+        <v>0.3331267748877192</v>
       </c>
       <c r="G6" t="n">
-        <v>0.206759864603819</v>
+        <v>0.2184902659085067</v>
       </c>
     </row>
     <row r="7">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3280334697981756</v>
+        <v>0.3428730091129042</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2651635502093803</v>
+        <v>0.319488385997261</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3834636931695756</v>
+        <v>0.3580251638419423</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3039707478027194</v>
+        <v>0.3134162129093187</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2885028370322488</v>
+        <v>0.2991018270451535</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2609387103318444</v>
+        <v>0.3058278565801656</v>
       </c>
     </row>
     <row r="8">
@@ -617,22 +617,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4580200501253133</v>
+        <v>0.3902732797340641</v>
       </c>
       <c r="C8" t="n">
-        <v>0.457613301340847</v>
+        <v>0.3741575405899034</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2694235588972431</v>
+        <v>0.3214633916951208</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4125497772312564</v>
+        <v>0.3330834588458381</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2725563909774436</v>
+        <v>0.2882633285708152</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3579992979989737</v>
+        <v>0.3176225093070977</v>
       </c>
     </row>
     <row r="9">
@@ -642,22 +642,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.366119747698695</v>
+        <v>0.3692069536221809</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3803632501529566</v>
+        <v>0.3533099774506524</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3165739657515974</v>
+        <v>0.3591185030049704</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3209097426926273</v>
+        <v>0.3420794746927613</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3173062865497076</v>
+        <v>0.2716745433728487</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3168483203650063</v>
+        <v>0.3066028663415306</v>
       </c>
     </row>
   </sheetData>
